--- a/docs/criteria/Screener_Criteria.xlsx
+++ b/docs/criteria/Screener_Criteria.xlsx
@@ -209,10 +209,10 @@
     <t xml:space="preserve">Cash conversion</t>
   </si>
   <si>
-    <t xml:space="preserve">FCF / net income &gt;= 0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that profits must turn into cash, because his first test of a good company is a high return on capital in cash: cash delivered in a period divided by capital employed. A mentioned example: he put his own portfolio at about 25% on this measure (2022). Connor Haley states that free cash flow is a better guide than reported profits, because earnings and EBITDA "can be easily manipulated". No specific past example given.</t>
+    <t xml:space="preserve">(FCF - stock pay) / net income &gt;= 0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that profits must turn into cash, because his first test of a good company is a high return on capital in cash: cash delivered in a period divided by capital employed. A mentioned example: he put his own portfolio at about 25% on this measure (2022). Connor Haley states that free cash flow is a better guide than reported profits, because earnings and EBITDA "can be easily manipulated". No specific past example given. Jim Chanos states that stock pay is a real cost, because "It's compensation. You're diluting your shareholders by issuing them stock", yet it is routinely added back. No specific past example given; he said this of tech companies in general.</t>
   </si>
   <si>
     <t xml:space="preserve">Earnings quality.</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">Already profitable</t>
   </si>
   <si>
-    <t xml:space="preserve">TTM and last-FY EBITDA &gt; 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that already having positive EBITDA means the company is a proven business, not a cash burner, because most big winners were past the profit turning point and were not losing money and diluting shareholders to survive. A mentioned example: in Alta Fox's study of 104 multibaggers (2015-2020), 88% already had positive EBITDA five years earlier.</t>
+    <t xml:space="preserve">TTM and last-FY EBITDA &gt; 0 (EBIT &gt; 0 when D&amp;A &gt;= 50% of EBITDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that already having positive EBITDA means the company is a proven business, not a cash burner, because most big winners were past the profit turning point and were not losing money and diluting shareholders to survive. A mentioned example: in Alta Fox's study of 104 multibaggers (2015-2020), 88% already had positive EBITDA five years earlier. Tom Gayner states that EBITDA fits businesses with little capital spending but flatters capital-heavy ones, because when "the d number" is big, EBITDA stops describing what is really going on. A mentioned example: a radio station (EBITDA fair) versus a steel mill (EBITDA misleading). Nick Del Deo states that valuing a GPU cloud on EBITDA ignores "what it's costing you to create this thing". A mentioned example: CoreWeave, with very high EBITDA margins carried by depreciation (2025).</t>
   </si>
   <si>
     <t xml:space="preserve">Cuts cash-burning stories.</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">Valuation</t>
   </si>
   <si>
-    <t xml:space="preserve">EV / EBITDA &lt;= 20x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that a moderate EV/EBITDA means the thesis can work on profit growth alone, because "if your entire thesis rests on significant multiple expansion maybe it's not a great thesis". A mentioned example: in his study the median multibagger traded about 10x forward EBITDA five years earlier and re-rated to about 25x, with two-thirds of the return from multiple expansion. Chris Davis states that a reasonable starting multiple means your return is set by the business, because he assumes no re-rating: "We may get it, but it's nowhere in our models." A mentioned example: in 2026 his holdings at about 14x earnings offered a 7.5% earnings yield, versus about 3.8% for the market at 26x.</t>
+    <t xml:space="preserve">EV / EBITDA &lt;= 20x (EV / EBIT when D&amp;A &gt;= 50% of EBITDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that a moderate EV/EBITDA means the thesis can work on profit growth alone, because "if your entire thesis rests on significant multiple expansion maybe it's not a great thesis". A mentioned example: in his study the median multibagger traded about 10x forward EBITDA five years earlier and re-rated to about 25x, with two-thirds of the return from multiple expansion. Chris Davis states that a reasonable starting multiple means your return is set by the business, because he assumes no re-rating: "We may get it, but it's nowhere in our models." A mentioned example: in 2026 his holdings at about 14x earnings offered a 7.5% earnings yield, versus about 3.8% for the market at 26x. Tom Gayner states that EBITDA is "exactly inversely proportionate" in accuracy to how large depreciation is, because capital-heavy assets must be replaced. A mentioned example: radio station versus steel mill. So the screen values capital-heavy businesses on EV/EBIT.</t>
   </si>
   <si>
     <t xml:space="preserve">Return comes from growth, not multiple expansion.</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">H7</t>
   </si>
   <si>
-    <t xml:space="preserve">FCF / net income &gt;= 0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that turning profits into cash shows the returns are real, because he measures return on capital as cash delivered against the capital employed. A mentioned example: the MSCI World quality subset (high returns on capital, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Connor Haley states that free cash flow is the number to trust, because earnings and EBITDA, unlike free cash flow, "can be easily manipulated". No specific past example given.</t>
+    <t xml:space="preserve">(FCF - stock pay) / net income &gt;= 0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that turning profits into cash shows the returns are real, because he measures return on capital as cash delivered against the capital employed. A mentioned example: the MSCI World quality subset (high returns on capital, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Connor Haley states that free cash flow is the number to trust, because earnings and EBITDA, unlike free cash flow, "can be easily manipulated". No specific past example given. Jim Chanos states that stock pay must be counted as a cost, because "It's compensation. You're diluting your shareholders", even though cash flow statements add it back. No specific past example given.</t>
   </si>
   <si>
     <t xml:space="preserve">H8</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">O7</t>
   </si>
   <si>
-    <t xml:space="preserve">FCF / net income &gt;= 0.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that relying on free cash flow means trusting the number hardest to fake, because earnings and EBITDA "can be easily manipulated". No specific past example given. Terry Smith states that good cash conversion is a mark of quality, because profits only count if they arrive as cash, so he measures return on capital in cash. A mentioned example: the MSCI World quality subset (high returns, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Dan Sundheim states that profits that don't reconcile with the cash and unit economics can signal accounting abuse, because capitalizing costs that should be expensed lifts profit without bringing in cash. A mentioned example: Orthodontic Centers of America, where he found "the simplest form of accounting fraud".</t>
+    <t xml:space="preserve">(FCF - stock pay) / net income &gt;= 0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that relying on free cash flow means trusting the number hardest to fake, because earnings and EBITDA "can be easily manipulated". No specific past example given. Terry Smith states that good cash conversion is a mark of quality, because profits only count if they arrive as cash, so he measures return on capital in cash. A mentioned example: the MSCI World quality subset (high returns, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Dan Sundheim states that profits that don't reconcile with the cash and unit economics can signal accounting abuse, because capitalizing costs that should be expensed lifts profit without bringing in cash. A mentioned example: Orthodontic Centers of America, where he found "the simplest form of accounting fraud". Jim Chanos states that stock pay is a cost that cash flow hides, because "It's compensation. You're diluting your shareholders". No specific past example given.</t>
   </si>
   <si>
     <t xml:space="preserve">O8</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">Below a hard floor</t>
   </si>
   <si>
-    <t xml:space="preserve">Market cap &lt;= 1.0x net cash, or price &lt;= 1.0x tangible book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prem Watsa states that buying below cash per share gives you the rest of the business for free, because the cash alone covers the price, leaving plants and inventories as a bonus. A mentioned example: Fairfax bought Seagram at about $65 a share against roughly $70 of cash per share, and the stock doubled and tripled. Joel Greenblatt states that a stock selling at its cash, with a business not burning money, is a bargain worth a look, because management has no incentive to waste the cash and the business may turn into something: "almost like a free option". No specific past example given.</t>
+    <t xml:space="preserve">Market cap &lt;= 1.0x net cash, or price &lt;= 1.0x tangible book with tangible book per share not down over 3 yrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prem Watsa states that buying below cash per share gives you the rest of the business for free, because the cash alone covers the price, leaving plants and inventories as a bonus. A mentioned example: Fairfax bought Seagram at about $65 a share against roughly $70 of cash per share, and the stock doubled and tripled. Joel Greenblatt states that a stock selling at its cash, with a business not burning money, is a bargain worth a look, because management has no incentive to waste the cash and the business may turn into something: "almost like a free option". No specific past example given. Steve Eisman states that "buying a home builder below tangible book value ... when the builder is growing book value, usually works out", because a growing book shows the floor is real rather than eroding. A mentioned example: Meritage Homes below tangible book (2025).</t>
   </si>
   <si>
     <t xml:space="preserve">Hard downside floor (the thesis).</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">Something is breaking</t>
   </si>
   <si>
-    <t xml:space="preserve">&gt;= 2 of: growth &lt; half its 3-yr rate; gross margin down 3 yrs; op margin down &gt;= 5 pts; TTM loss; dilution &gt;= 5%/yr; shrinking revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Einhorn states that a short needs "over valuation combined with some kind of deterioration", because an expensive stock can stay expensive until the business visibly weakens. A mentioned example: in his bubble basket he would change his view on names once they "start showing real profits". Steve Cohen states that slowing growth on a high multiple is "a mix that doesn't give you much upside", because the price still assumes growth that is fading. No specific past example given; he said this of the market in May 2025.</t>
+    <t xml:space="preserve">&gt;= 2 of: growth &lt; half its 3-yr rate; gross margin down 3 yrs; op margin down &gt;= 5 pts; TTM loss; dilution &gt;= 5%/yr; shrinking revenue; profits above cash 2 yrs; negative operating cash flow; restructuring in &gt;= 4 of 5 yrs; acquisitions &gt; operating cash flow (3 yrs); inventory days at 5-yr high; heavy capex with negative FCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Einhorn states that a short needs "over valuation combined with some kind of deterioration", because an expensive stock can stay expensive until the business visibly weakens. A mentioned example: in his bubble basket he would change his view on names once they "start showing real profits". Steve Cohen states that slowing growth on a high multiple is "a mix that doesn't give you much upside", because the price still assumes growth that is fading. No specific past example given; he said this of the market in May 2025. Jim Chanos states that "a lot of frauds have negative cash flow or have growing by acquisition", and that restructuring charges taken "10 out of the last 12 years" are not non-recurring. A mentioned example: IBM's recurring restructuring charges. Gavin Baker states that inventories at record highs warned of a downturn. A mentioned example: his February 2000 semiconductor sell call, when "days inventory were at all-time highs".</t>
   </si>
   <si>
     <t xml:space="preserve">Second half of the avoid case.</t>
@@ -2772,7 +2772,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>82</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>252</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
         <v>354</v>
       </c>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I103" s="4"/>
     </row>
-    <row r="104" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>420</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
         <v>533</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
         <v>533</v>
       </c>

--- a/docs/criteria/Screener_Criteria.xlsx
+++ b/docs/criteria/Screener_Criteria.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Criteria!$A$1:$I$140</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Unverifiable!$A$1:$F$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Criteria!$A$1:$I$141</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Unverifiable!$A$1:$F$53</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="646">
   <si>
     <t xml:space="preserve">Screen</t>
   </si>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">H4</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;= 1 loss year in last 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that steady profits mark a proven business rather than a cash burner, because a company already making money does not need to keep raising cash and diluting owners. A mentioned example: in Alta Fox's study of 104 multibaggers (2015–20), most were profitable five years earlier, "relatively proven concepts" that "weren't losing millions".</t>
+    <t xml:space="preserve">&lt;= 1 loss year in last 5 (not applied to a new launcher: profitable now, revenue CAGR &gt;= 25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that steady profits mark a proven business rather than a cash burner, because a company already making money does not need to keep raising cash and diluting owners. A mentioned example: in Alta Fox's study of 104 multibaggers (2015–20), most were profitable five years earlier, "relatively proven concepts" that "weren't losing millions". Rod Wong states that the opportunity now lies in companies moving from development to sales, because "the biggest opportunity is actually in smaller but mid to late stage development or early stage commercial publicly traded companies". So a new launcher, profitable now and growing fast, is not judged on its development-stage losses. No specific past example given.</t>
   </si>
   <si>
     <t xml:space="preserve">H5</t>
@@ -836,316 +836,334 @@
     <t xml:space="preserve">High returns</t>
   </si>
   <si>
+    <t xml:space="preserve">10-yr median ROIC &gt;= 12% (not applied to a new launcher)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that a high return on capital marks a quality business, because return on capital is "the single most important thing" and high returns persist for decades. A mentioned example: pharmaceuticals and health care are among the sectors with high returns on capital in both 1963–2004 and the latest 20 years. Joel Greenblatt states that a pre-tax return of 14% is generally not good, while 20% pre-tax, about 12% after a 40% tax, is decent though not amazing, because it leaves room for error. No specific past example given. Rod Wong describes "a new wave or a new generation of commercially successful biotech companies", whose 10-year returns still reflect the development years; a new launcher is therefore exempt. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moat evidence (patents, installed base).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin (products)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin &gt;= 65% for drug makers (SIC 2833-2836), &gt;= 50% for devices and tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bihua Chen states that a high gross margin is what a real drug business looks like, because a pharmaceutical company's gross margin should be 80 to 90%, with operating margin up to about 50% depending on marketing costs and efficiency. No specific past example given. The screen applies her range to drug makers at 65% (diversified groups with device arms run in the high 60s) and keeps 50% for devices and tools.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pricing power.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare: no gross-profit line (e.g. REGN) -&gt; no data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(FCF - stock pay) / net income &gt;= 0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that turning profits into cash shows the returns are real, because he measures return on capital as cash delivered against the capital employed. A mentioned example: the MSCI World quality subset (high returns on capital, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Connor Haley states that free cash flow is the number to trust, because earnings and EBITDA, unlike free cash flow, "can be easily manipulated". No specific past example given. Jim Chanos states that stock pay must be counted as a cost, because "It's compensation. You're diluting your shareholders", even though cash flow statements add it back. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt / EBITDA &lt;= 3x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that debt taken on to buy another business makes a company fragile, because a sudden shock can leave it short of cash and facing bankruptcy. A mentioned example: Alta Fox sold a well-run restaurant stock that had just levered up for an acquisition right before COVID; it survived, but he defends the sale. Brian Gaines states that heavy debt turns the shares into an option bet, because banks can force a bankruptcy in a bad patch, so share-price moves say little about the company's value. A mentioned example: Movie Gallery, with $1.1 billion of debt and about 30 million shares, fell to $6.80 by late 2005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue CAGR &gt;= 3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that growing sales show a company can reinvest its high returns, because high returns are wasted in a business that can't grow; he wants secular growth, where each cycle's peak and trough beat the last. No specific past example given. Jim Flynn states that shrinking sales at a drug company can mean a patent has expired, because "a generic will get 98% of volume within a month" after a patent ends, so branded revenue is close to all-or-nothing. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franchise still growing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that the first question is how good the business is, because a low price can't make a bad company good: "It may give you a short-term opportunity, but it certainly doesn't give you a long-term one." A mentioned example: low-return sectors such as utilities, telecoms, transport and retailing stayed low for decades. Chris Davis states that business quality outweighs entry price for a long-term owner, because "your return over time is going to approach the return on equity of the business, no matter what your starting price is." No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare - Clinical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharma/biotech/device SIC codes, not commercial-stage (revenue &lt; $200M or operating loss)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bihua Chen states that a pre-revenue biotech can't be judged on earnings, because its value turns on whether the drug works; projecting cash flows and comparing peers is the "less value added" part. A mentioned example: an Alzheimer's antibiotic theory built on a correlation failed an adequately sized placebo-controlled trial. Connor Haley states that requiring positive trailing EBITDA removes biotech from a generalist screen, because such companies "aren't in sort of the generalist investor framework". A mentioned example: Alta Fox's 2020 multibagger study used exactly this filter to take biotech out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate 'cash floor + option' logic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recent balance sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sheet &lt;= 200 days old</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No investor source: clinical companies burn cash quickly, so the cash figure is only useful if the balance sheet is recent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accurate floor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash runway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash / annual burn &gt;= 2 yrs (near miss if the 2-yr funding gap &lt;= 20% of market cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bihua Chen states that cash burn makes biotech prices depend on financing, because biotechs are long-dated assets that "burn a lot of money" under "a lot of financing pressure", so she passes when there isn't enough capital to reach the next proof point. No specific past example given. Jim Flynn states that cash-hungry biotechs listed in a bubble tend not to last, because bubbles let in companies that are "too early, too risky, require too much cash", and they "just have to go away". A mentioned example: in May 2025 biotech had just been through his third bubble and collapse in 36 years. Eli Casdin states that a long cash runway keeps a company from failing for lack of money, because he is "over capitalizing these businesses so they're not going to run out of money", scaling up his investment over time instead of putting everything in first and fighting dilution on the way down. A mentioned example: his companies burn about $100–150 million every 12–24 months (2022). Rod Wong states that a company can normally raise only a slice of its value at once, because "you can do an equity offering for like 10 to 20 percent of a company's market cap". So a company whose 2-year funding gap fits in one such raise is a near miss rather than a reject. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to reach the next catalyst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn = last 12 months operating cash flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Little debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt / cash &lt;= 0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dave Johnson states that a convertible bond ahead of shareholders weighs on the stock, because it is a claim on the company's cash. A mentioned example: MorphoSys's convertible traded at a big discount, and within about six weeks of Caligan's push the company bought back about 25% of it (2023). Jim Flynn states that senior secured debt comes ahead of shareholders, because the lender's part "protects your basis" and lets the lender take control if the company fails. A mentioned example: when COVID nearly sank Melinta, Deerfield, as secured lender, credit-bid, took over the company and later sold it for over $300 million.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor belongs to shareholders.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market cap &gt;= $50M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No investor source: below about $50M of market value a stock is hard to buy without moving the price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that a minimum daily trading value makes a stock practical to own, because a fund needs enough trading to build and exit a position. A mentioned example: Alta Fox's multibagger study required average daily value traded over $200,000, "reasonably liquid" for a small and micro cap investor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / cash &lt;= 0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dave Johnson states that an enterprise value near or below cash means you get the drug pipeline almost free, because cash and approved assets already cover the price. A mentioned example: MorphoSys had negative EV from December 2022 with about €1 billion of cash: "you own this option for nothing". Joel Greenblatt states that a stock priced at its cash, with a business not burning money, comes almost free, because management has no incentive to waste the cash and the business may turn into something: "almost like a free option". No specific past example given. The RA Capital panel (Peter Kolchinsky and colleagues) states that a biotech below cash has a floor, because "If they're trading below cash, odds are they're probably not going to go to zero". A mentioned example: 214 of about 660 biotechs traded below cash at the time of the talk (2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard downside floor + free upside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor after a year of burn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market cap / (cash - debt - one year of burn) &lt;= 1.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dave Johnson's interviewer, summarizing Caligan's case, states that the floor is measured after the coming burn, because "more than half of that value would be covered by the net cash at the end of this year so after 200 million plus of cash burn". A mentioned example: MorphoSys at about €27 a share in 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor net of burn and debt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclicals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity-cycle industries: metals, energy, chemicals, building materials, homebuilders, machinery, semis, autos, transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley Druckenmiller states that capacity-cycle industries need cycle-aware rules, because when companies lose money capacity shrinks and margins recover within about three years, while flush industries announce expansions that bring margins down. A mentioned example: chemicals, his early sector, where you bought when everyone was losing money and shutting capacity. Connor Haley states that a cyclical company must be judged on trough numbers, because its profits swing with the cycle, so he wants it at a trough multiple on trough margins. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right yardstick for cyclicals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Greenblatt states that a long record means you can see the bad years and find normal earnings, because good and bad years must be averaged: $10 a year for nine years plus one break-even year is about $9. A mentioned example: Wells Fargo could earn about $18 a share in a normal year yet roughly zero once every seven or eight years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enables cycle-average figures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No investor source: a data and ownership rule, because tiny filers have patchier numbers and are hard to own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-cycle returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Davis states that solid returns on capital mean the business, not the entry price, drives a long-term owner's return, because "your return over time is going to approach the return on equity of the business, no matter what your starting price is." A mentioned example: buy a business at half of book that keeps reinvesting at 4%, and your return heads toward 4%. Terry Smith states that a good return record means a good business, because returns on capital stay persistent for decades and a low rating does not turn a bad company into a good one. A mentioned example: in his sector data, transport, energy and materials stayed persistently low-return groups.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality filter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survives downturns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;= 7 profitable (EBIT) years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Greenblatt states that staying profitable in bad years means a cyclical is worth more than its swings suggest, because a business that does not lose money in a bust keeps its earning power and survives. A mentioned example: NVR, a homebuilder with pre-sold homes and little capital tied up, which in a downturn might take a small hit but probably would not lose money.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survival.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt / avg EBITDA (cycle) &lt;= 2.5x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Greenblatt states that low debt matters most in cyclicals, because whether a company survives the cycle depends on how leveraged it is, and you don't want to lever up a very cyclical business. No specific past example given. Brian Gaines states that heavy debt turns the equity into "an option bet", because banks can force a levered company into bankruptcy in a bad stretch. A mentioned example: Movie Gallery, with $1.1 billion of debt on about 30 million shares. Connor Haley states that a strong balance sheet means downside protection, because it lets a company survive a shock. A mentioned example: in March 2020 Alta Fox sold a restaurant stock that had just borrowed for an acquisition before COVID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survives the next downturn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not at peak margins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest margin in lower half of own 10-yr range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley Druckenmiller states that buying when margins are low means buying before the recovery, because "when companies are losing money, capacity is always going to shrink and their margins going to look better in 3 years", while over-earners' margins come down. A mentioned example: in 2022 he named ocean shipping, with "massive margins", among the true over-earners, after retail and trucking. Connor Haley states that a cyclical should be bought at trough margins, because buying near peak margins means buying profits that will shrink. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle timing (core of the thesis).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own history only; industry capacity cycle isn't measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap on normalized earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / 10-yr avg EBIT &lt;= 12x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Greenblatt states that a low price on cycle-average earnings means a real bargain, because he draws the normal earnings line through good and bad years and pays a low multiple on it, instead of trusting one year. A mentioned example: Wells Fargo, with normalized earnings near $16 a share at about $70, dipped to $60 and later reached $250. Connor Haley states that a cyclical should trade at a trough multiple on trough margins, because then the price already assumes the bad part of the cycle. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin of safety if the cycle turns slowly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-Operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that leaving out utilities, telecoms, transport, energy, materials and retailing means skipping businesses whose returns stay low, because returns on capital persist for decades and being cheap doesn't turn a bad company into a good one. A mentioned example: airlines, which he says never make an adequate return on capital. Chris Hohn states that avoiding banks, autos, retail, insurance, commodities, airlines, telecoms and media means skipping businesses without real barriers to entry, because growth without barriers earns little for owners. A mentioned example: airlines grew about 5% a year for a century with minimal profit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Smith states that a long record of returns means you can tell a truly good company from a lucky one, because high and low returns on capital tend to persist for decades. A mentioned example: return-on-equity data back to 1966, where the high-return group kept clustering around 20% and stayed well above the low group. Joel Greenblatt states that one year of high returns proves little, because last year's return on capital may be a cyclical peak or include one-off items, so it may not be the return going forward. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No investor source: old filings can hide a recent collapse, so the screen only uses companies with a fresh annual report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue &gt;= $50M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No investor source: very small filers have patchy data and are hard to own in a meaningful size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider share &gt;= 20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Stahl states that high insider ownership means an owner-operator, someone who runs the company because they own more of it than anyone else, because their wealth moves with the shares; float-weighted indexes also underweight such firms, leaving them cheaper. A mentioned example: his S&amp;P 500 study back to 1957, where owner-operators earned the bulk of the return. Chris Davis states that managers who are real owners means incentives are aligned with shareholders, because managers who aren't owners chase the most pay possible, which is an expense for owners; "We want to invest in owner-operators." No specific past example given. Connor Haley states that management owning at least about 5% in small and micro caps means they care about shareholders, because their own net worth rises and falls with the stock. A mentioned example: XPEL's CEO Ryan Pape keeps a material part of his net worth in the stock and, Haley believes, has never sold a share.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alignment + under-owned by index funds (cheaper).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From cover-page public float. Foreign filers report none (~43); no share count near float date (~29); share-class mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;= 2 operating-loss years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Haley states that a record of profits means a proven business rather than a cash burner, because companies already making money don't need to dilute shareholders to survive and can grow into operating leverage. A mentioned example: Alta Fox's study of 104 multibaggers from 2015-20, most of which were already profitable five years before their big run. Joel Greenblatt states that a single bad year should not disqualify a steady business, because what matters is normalized earnings across years: a company earning $10 for nine years and breaking even in one is worth roughly $9 of normal earnings. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O6</t>
+  </si>
+  <si>
     <t xml:space="preserve">10-yr median ROIC &gt;= 12%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that a high return on capital marks a quality business, because return on capital is "the single most important thing" and high returns persist for decades. A mentioned example: pharmaceuticals and health care are among the sectors with high returns on capital in both 1963–2004 and the latest 20 years. Joel Greenblatt states that a pre-tax return of 14% is generally not good, while 20% pre-tax, about 12% after a 40% tax, is decent though not amazing, because it leaves room for error. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moat evidence (patents, installed base).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross margin (products)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross margin &gt;= 50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bihua Chen states that a high gross margin is what a real drug business looks like, because a pharmaceutical company's gross margin should be 80 to 90%, with operating margin up to about 50% depending on marketing costs and efficiency. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pricing power.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare: no gross-profit line (e.g. REGN) -&gt; no data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(FCF - stock pay) / net income &gt;= 0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that turning profits into cash shows the returns are real, because he measures return on capital as cash delivered against the capital employed. A mentioned example: the MSCI World quality subset (high returns on capital, high margins, good cash conversion) beat the index in every rolling 10-year period since 1996. Connor Haley states that free cash flow is the number to trust, because earnings and EBITDA, unlike free cash flow, "can be easily manipulated". No specific past example given. Jim Chanos states that stock pay must be counted as a cost, because "It's compensation. You're diluting your shareholders", even though cash flow statements add it back. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net debt / EBITDA &lt;= 3x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that debt taken on to buy another business makes a company fragile, because a sudden shock can leave it short of cash and facing bankruptcy. A mentioned example: Alta Fox sold a well-run restaurant stock that had just levered up for an acquisition right before COVID; it survived, but he defends the sale. Brian Gaines states that heavy debt turns the shares into an option bet, because banks can force a bankruptcy in a bad patch, so share-price moves say little about the company's value. A mentioned example: Movie Gallery, with $1.1 billion of debt and about 30 million shares, fell to $6.80 by late 2005.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue CAGR &gt;= 3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that growing sales show a company can reinvest its high returns, because high returns are wasted in a business that can't grow; he wants secular growth, where each cycle's peak and trough beat the last. No specific past example given. Jim Flynn states that shrinking sales at a drug company can mean a patent has expired, because "a generic will get 98% of volume within a month" after a patent ends, so branded revenue is close to all-or-nothing. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franchise still growing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that the first question is how good the business is, because a low price can't make a bad company good: "It may give you a short-term opportunity, but it certainly doesn't give you a long-term one." A mentioned example: low-return sectors such as utilities, telecoms, transport and retailing stayed low for decades. Chris Davis states that business quality outweighs entry price for a long-term owner, because "your return over time is going to approach the return on equity of the business, no matter what your starting price is." No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Healthcare - Clinical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharma/biotech/device SIC codes, not commercial-stage (revenue &lt; $200M or operating loss)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bihua Chen states that a pre-revenue biotech can't be judged on earnings, because its value turns on whether the drug works; projecting cash flows and comparing peers is the "less value added" part. A mentioned example: an Alzheimer's antibiotic theory built on a correlation failed an adequately sized placebo-controlled trial. Connor Haley states that requiring positive trailing EBITDA removes biotech from a generalist screen, because such companies "aren't in sort of the generalist investor framework". A mentioned example: Alta Fox's 2020 multibagger study used exactly this filter to take biotech out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Separate 'cash floor + option' logic.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recent balance sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance sheet &lt;= 200 days old</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No investor source: clinical companies burn cash quickly, so the cash figure is only useful if the balance sheet is recent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accurate floor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash runway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash / annual burn &gt;= 2 yrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bihua Chen states that cash burn makes biotech prices depend on financing, because biotechs are long-dated assets that "burn a lot of money" under "a lot of financing pressure", so she passes when there isn't enough capital to reach the next proof point. No specific past example given. Jim Flynn states that cash-hungry biotechs listed in a bubble tend not to last, because bubbles let in companies that are "too early, too risky, require too much cash", and they "just have to go away". A mentioned example: in May 2025 biotech had just been through his third bubble and collapse in 36 years. Eli Casdin states that a long cash runway keeps a company from failing for lack of money, because he is "over capitalizing these businesses so they're not going to run out of money", scaling up his investment over time instead of putting everything in first and fighting dilution on the way down. A mentioned example: his companies burn about $100–150 million every 12–24 months (2022).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time to reach the next catalyst.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burn = last 12 months operating cash flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Little debt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt / cash &lt;= 0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dave Johnson states that a convertible bond ahead of shareholders weighs on the stock, because it is a claim on the company's cash. A mentioned example: MorphoSys's convertible traded at a big discount, and within about six weeks of Caligan's push the company bought back about 25% of it (2023). Jim Flynn states that senior secured debt comes ahead of shareholders, because the lender's part "protects your basis" and lets the lender take control if the company fails. A mentioned example: when COVID nearly sank Melinta, Deerfield, as secured lender, credit-bid, took over the company and later sold it for over $300 million.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor belongs to shareholders.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market cap &gt;= $50M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No investor source: below about $50M of market value a stock is hard to buy without moving the price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that a minimum daily trading value makes a stock practical to own, because a fund needs enough trading to build and exit a position. A mentioned example: Alta Fox's multibagger study required average daily value traded over $200,000, "reasonably liquid" for a small and micro cap investor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV / cash &lt;= 0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dave Johnson states that an enterprise value near or below cash means you get the drug pipeline almost free, because cash and approved assets already cover the price. A mentioned example: MorphoSys had negative EV from December 2022 with about €1 billion of cash: "you own this option for nothing". Joel Greenblatt states that a stock priced at its cash, with a business not burning money, comes almost free, because management has no incentive to waste the cash and the business may turn into something: "almost like a free option". No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard downside floor + free upside.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclicals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity-cycle industries: metals, energy, chemicals, building materials, homebuilders, machinery, semis, autos, transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley Druckenmiller states that capacity-cycle industries need cycle-aware rules, because when companies lose money capacity shrinks and margins recover within about three years, while flush industries announce expansions that bring margins down. A mentioned example: chemicals, his early sector, where you bought when everyone was losing money and shutting capacity. Connor Haley states that a cyclical company must be judged on trough numbers, because its profits swing with the cycle, so he wants it at a trough multiple on trough margins. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Right yardstick for cyclicals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Greenblatt states that a long record means you can see the bad years and find normal earnings, because good and bad years must be averaged: $10 a year for nine years plus one break-even year is about $9. A mentioned example: Wells Fargo could earn about $18 a share in a normal year yet roughly zero once every seven or eight years.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enables cycle-average figures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No investor source: a data and ownership rule, because tiny filers have patchier numbers and are hard to own.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid-cycle returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Davis states that solid returns on capital mean the business, not the entry price, drives a long-term owner's return, because "your return over time is going to approach the return on equity of the business, no matter what your starting price is." A mentioned example: buy a business at half of book that keeps reinvesting at 4%, and your return heads toward 4%. Terry Smith states that a good return record means a good business, because returns on capital stay persistent for decades and a low rating does not turn a bad company into a good one. A mentioned example: in his sector data, transport, energy and materials stayed persistently low-return groups.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality filter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Survives downturns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;= 7 profitable (EBIT) years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Greenblatt states that staying profitable in bad years means a cyclical is worth more than its swings suggest, because a business that does not lose money in a bust keeps its earning power and survives. A mentioned example: NVR, a homebuilder with pre-sold homes and little capital tied up, which in a downturn might take a small hit but probably would not lose money.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Survival.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net debt / avg EBITDA (cycle) &lt;= 2.5x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Greenblatt states that low debt matters most in cyclicals, because whether a company survives the cycle depends on how leveraged it is, and you don't want to lever up a very cyclical business. No specific past example given. Brian Gaines states that heavy debt turns the equity into "an option bet", because banks can force a levered company into bankruptcy in a bad stretch. A mentioned example: Movie Gallery, with $1.1 billion of debt on about 30 million shares. Connor Haley states that a strong balance sheet means downside protection, because it lets a company survive a shock. A mentioned example: in March 2020 Alta Fox sold a restaurant stock that had just borrowed for an acquisition before COVID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Survives the next downturn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not at peak margins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest margin in lower half of own 10-yr range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley Druckenmiller states that buying when margins are low means buying before the recovery, because "when companies are losing money, capacity is always going to shrink and their margins going to look better in 3 years", while over-earners' margins come down. A mentioned example: in 2022 he named ocean shipping, with "massive margins", among the true over-earners, after retail and trucking. Connor Haley states that a cyclical should be bought at trough margins, because buying near peak margins means buying profits that will shrink. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle timing (core of the thesis).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own history only; industry capacity cycle isn't measured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap on normalized earnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EV / 10-yr avg EBIT &lt;= 12x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Greenblatt states that a low price on cycle-average earnings means a real bargain, because he draws the normal earnings line through good and bad years and pays a low multiple on it, instead of trusting one year. A mentioned example: Wells Fargo, with normalized earnings near $16 a share at about $70, dipped to $60 and later reached $250. Connor Haley states that a cyclical should trade at a trough multiple on trough margins, because then the price already assumes the bad part of the cycle. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin of safety if the cycle turns slowly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner-Operators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that leaving out utilities, telecoms, transport, energy, materials and retailing means skipping businesses whose returns stay low, because returns on capital persist for decades and being cheap doesn't turn a bad company into a good one. A mentioned example: airlines, which he says never make an adequate return on capital. Chris Hohn states that avoiding banks, autos, retail, insurance, commodities, airlines, telecoms and media means skipping businesses without real barriers to entry, because growth without barriers earns little for owners. A mentioned example: airlines grew about 5% a year for a century with minimal profit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Smith states that a long record of returns means you can tell a truly good company from a lucky one, because high and low returns on capital tend to persist for decades. A mentioned example: return-on-equity data back to 1966, where the high-return group kept clustering around 20% and stayed well above the low group. Joel Greenblatt states that one year of high returns proves little, because last year's return on capital may be a cyclical peak or include one-off items, so it may not be the return going forward. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No investor source: old filings can hide a recent collapse, so the screen only uses companies with a fresh annual report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue &gt;= $50M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No investor source: very small filers have patchy data and are hard to own in a meaningful size.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insider ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insider share &gt;= 20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Stahl states that high insider ownership means an owner-operator, someone who runs the company because they own more of it than anyone else, because their wealth moves with the shares; float-weighted indexes also underweight such firms, leaving them cheaper. A mentioned example: his S&amp;P 500 study back to 1957, where owner-operators earned the bulk of the return. Chris Davis states that managers who are real owners means incentives are aligned with shareholders, because managers who aren't owners chase the most pay possible, which is an expense for owners; "We want to invest in owner-operators." No specific past example given. Connor Haley states that management owning at least about 5% in small and micro caps means they care about shareholders, because their own net worth rises and falls with the stock. A mentioned example: XPEL's CEO Ryan Pape keeps a material part of his net worth in the stock and, Haley believes, has never sold a share.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alignment + under-owned by index funds (cheaper).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From cover-page public float. Foreign filers report none (~43); no share count near float date (~29); share-class mismatches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;= 2 operating-loss years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Haley states that a record of profits means a proven business rather than a cash burner, because companies already making money don't need to dilute shareholders to survive and can grow into operating leverage. A mentioned example: Alta Fox's study of 104 multibaggers from 2015-20, most of which were already profitable five years before their big run. Joel Greenblatt states that a single bad year should not disqualify a steady business, because what matters is normalized earnings across years: a company earning $10 for nine years and breaking even in one is worth roughly $9 of normal earnings. No specific past example given.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O6</t>
   </si>
   <si>
     <t xml:space="preserve">Terry Smith states that a high return on capital means a business can compound in value, because over a long holding your return converges on what the business earns on its capital; he calls return on capital "the single most important thing". A mentioned example: airlines, which he says never make an adequate return on capital. Joel Greenblatt states that a high return on tangible capital means a good business, because it shows the profit on each dollar tied up in the business: pre-tax 14% is generally not good, while 20% (about 12% after tax) is decent. A mentioned example: Moody's, which needed no reinvestment and was the best business he had ever found.</t>
@@ -2505,7 +2523,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -4020,7 +4038,7 @@
       </c>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>252</v>
       </c>
@@ -4047,7 +4065,7 @@
       </c>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>252</v>
       </c>
@@ -4076,7 +4094,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>252</v>
       </c>
@@ -4275,7 +4293,7 @@
       </c>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>290</v>
       </c>
@@ -4387,7 +4405,7 @@
       </c>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>290</v>
       </c>
@@ -4416,159 +4434,159 @@
         <v>138</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="D69" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" s="4" t="s">
+      <c r="F69" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C69" s="2" t="s">
+    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F70" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" s="4" t="s">
+      <c r="H71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C71" s="2" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G71" s="4" t="s">
+      <c r="F72" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="H72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -4582,52 +4600,52 @@
       <c r="H73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>339</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>346</v>
@@ -4639,831 +4657,831 @@
         <v>15</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>348</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="F77" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I76" s="4" t="s">
+      <c r="I77" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B77" s="3" t="s">
+    <row r="78" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D78" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G77" s="4" t="s">
+      <c r="F78" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="4" t="s">
+      <c r="H78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C78" s="2" t="s">
+    <row r="79" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="B80" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="4" t="s">
+      <c r="H80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C80" s="2" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E80" s="3" t="s">
+      <c r="D81" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G80" s="4" t="s">
+      <c r="F81" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>367</v>
-      </c>
       <c r="H81" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="4"/>
+    </row>
+    <row r="82" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>370</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>371</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>220</v>
+        <v>372</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>374</v>
+        <v>220</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>59</v>
+        <v>268</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G84" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" s="4" t="s">
+      <c r="H85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C85" s="2" t="s">
+    <row r="86" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="F86" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" s="4" t="s">
+      <c r="H86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C86" s="2" t="s">
+    <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D87" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G87" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="H88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="E88" s="3" t="s">
+      <c r="D89" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="H88" s="3" t="s">
+      <c r="F89" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I88" s="4" t="s">
+      <c r="I89" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B89" s="3" t="s">
+    <row r="90" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="E89" s="3" t="s">
+      <c r="D90" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="F90" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D91" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="4"/>
-    </row>
-    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>27</v>
+        <v>259</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="I91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="E92" s="3" t="s">
+      <c r="D93" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G92" s="4" t="s">
+      <c r="F93" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="4"/>
-    </row>
-    <row r="93" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E93" s="3" t="s">
+      <c r="H93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="4" t="s">
+      <c r="F94" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="4"/>
-    </row>
-    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>36</v>
+        <v>411</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C96" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D97" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E97" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="G96" s="4" t="s">
+      <c r="F97" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="G97" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" s="4" t="s">
+      <c r="H97" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C97" s="2" t="s">
+    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>383</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G98" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="4"/>
-    </row>
-    <row r="99" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="H99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="D100" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="H99" s="3" t="s">
+      <c r="F100" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I99" s="4" t="s">
+      <c r="I100" s="4" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>425</v>
+        <v>10</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" s="4"/>
-    </row>
-    <row r="102" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D102" s="4" t="s">
-        <v>25</v>
+        <v>432</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>261</v>
+        <v>433</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>27</v>
+        <v>259</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I102" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>295</v>
+        <v>24</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>296</v>
+        <v>25</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="G103" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="G104" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="H103" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I103" s="4"/>
-    </row>
-    <row r="104" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="H104" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+      <c r="I104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>437</v>
@@ -5475,7 +5493,7 @@
         <v>439</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>440</v>
@@ -5484,31 +5502,33 @@
         <v>441</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I105" s="4"/>
-    </row>
-    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>15</v>
@@ -5517,260 +5537,258 @@
     </row>
     <row r="107" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D108" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="G107" s="4" t="s">
+      <c r="F108" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G108" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H107" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I107" s="4" t="s">
+      <c r="H108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="4" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I108" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F109" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G110" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H109" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109" s="4"/>
-    </row>
-    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B110" s="3" t="s">
+      <c r="H110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E110" s="3" t="s">
+      <c r="D111" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F110" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" s="4" t="s">
+      <c r="F111" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C111" s="2" t="s">
+    <row r="112" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I111" s="4"/>
-    </row>
-    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D112" s="4" t="s">
-        <v>25</v>
+        <v>462</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G112" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H112" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" s="4" t="s">
+      <c r="H113" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I113" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C113" s="2" t="s">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D114" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E114" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G113" s="4" t="s">
+      <c r="F114" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G114" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H113" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I113" s="4"/>
-    </row>
-    <row r="114" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="E114" s="3" t="s">
+      <c r="H114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" s="4"/>
+    </row>
+    <row r="115" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E115" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F114" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I114" s="4"/>
-    </row>
-    <row r="115" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F115" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I115" s="4" t="s">
-        <v>470</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I115" s="4"/>
     </row>
     <row r="116" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>471</v>
@@ -5797,264 +5815,264 @@
         <v>476</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>477</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D117" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="E117" s="3" t="s">
+      <c r="D118" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="G117" s="4" t="s">
+      <c r="F118" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G118" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H117" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117" s="4" t="s">
+      <c r="H118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I118" s="4" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>485</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>133</v>
+        <v>486</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>183</v>
+        <v>489</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>151</v>
+        <v>492</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G120" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G121" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H120" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I120" s="4"/>
-    </row>
-    <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>495</v>
-      </c>
       <c r="H121" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I121" s="4" t="s">
-        <v>496</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I121" s="4"/>
     </row>
     <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>498</v>
       </c>
       <c r="E122" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F122" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I122" s="4"/>
-    </row>
-    <row r="123" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="C123" s="2" t="s">
+      <c r="D123" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I123" s="4"/>
+    </row>
+    <row r="124" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D124" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I123" s="4"/>
-    </row>
-    <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>459</v>
+        <v>508</v>
       </c>
       <c r="G124" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="4"/>
+    </row>
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G125" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H124" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I124" s="4" t="s">
+      <c r="H125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I125" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I125" s="4" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>510</v>
@@ -6063,128 +6081,128 @@
         <v>511</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>166</v>
+        <v>512</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I126" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>516</v>
+        <v>166</v>
       </c>
       <c r="E127" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I127" s="4"/>
+    </row>
+    <row r="128" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="E128" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F127" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I127" s="4"/>
-    </row>
-    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F128" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>62</v>
+        <v>524</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I128" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="4"/>
+    </row>
+    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>217</v>
+        <v>526</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G130" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I129" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>15</v>
@@ -6193,56 +6211,56 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C131" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D132" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E132" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F131" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I131" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F132" s="4" t="s">
-        <v>487</v>
+        <v>535</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>183</v>
+        <v>536</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>75</v>
@@ -6251,81 +6269,83 @@
         <v>138</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G133" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H133" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I133" s="4"/>
-    </row>
-    <row r="134" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B134" s="3" t="s">
+      <c r="H134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="4"/>
+    </row>
+    <row r="135" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D134" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="E134" s="3" t="s">
+      <c r="D135" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I134" s="4"/>
-    </row>
-    <row r="135" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F135" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>259</v>
+        <v>542</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>15</v>
@@ -6334,150 +6354,177 @@
     </row>
     <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>25</v>
+        <v>432</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>459</v>
+        <v>544</v>
       </c>
       <c r="G136" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I136" s="4"/>
+    </row>
+    <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H136" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I136" s="4" t="s">
+      <c r="H137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I137" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E137" s="3" t="s">
+    <row r="138" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="E138" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F137" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I137" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="F138" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>551</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>133</v>
+        <v>552</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>489</v>
+        <v>559</v>
       </c>
       <c r="G140" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G141" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H140" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I140" s="4"/>
+      <c r="H141" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I141" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I140"/>
-  <conditionalFormatting sqref="H2:H140">
+  <autoFilter ref="A1:I141"/>
+  <conditionalFormatting sqref="H2:H141">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$H2="Easy"</formula>
     </cfRule>
@@ -6491,7 +6538,7 @@
       <formula>$H2="n/a"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:I140">
+  <conditionalFormatting sqref="A2:I141">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$E2="Valuation"</formula>
     </cfRule>
@@ -6528,19 +6575,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6548,19 +6595,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6568,19 +6615,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6588,19 +6635,19 @@
         <v>154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6608,19 +6655,19 @@
         <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6628,19 +6675,19 @@
         <v>252</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6648,164 +6695,164 @@
         <v>290</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>571</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>567</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>571</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -6815,7 +6862,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -6825,7 +6872,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -6854,7 +6901,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -6873,16 +6920,16 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6890,19 +6937,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6910,19 +6957,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6930,19 +6977,19 @@
         <v>82</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6950,19 +6997,19 @@
         <v>154</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6970,19 +7017,19 @@
         <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6990,19 +7037,19 @@
         <v>186</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7010,19 +7057,19 @@
         <v>252</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7030,19 +7077,19 @@
         <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7050,179 +7097,179 @@
         <v>290</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7236,13 +7283,13 @@
         <v>72</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>76</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7256,13 +7303,13 @@
         <v>106</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>109</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7276,13 +7323,13 @@
         <v>123</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7296,13 +7343,13 @@
         <v>134</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7316,13 +7363,13 @@
         <v>141</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7336,13 +7383,13 @@
         <v>146</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7356,13 +7403,13 @@
         <v>156</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>160</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7376,13 +7423,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>163</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7396,13 +7443,13 @@
         <v>166</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>169</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7416,13 +7463,13 @@
         <v>176</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>179</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7436,13 +7483,13 @@
         <v>181</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7456,13 +7503,13 @@
         <v>203</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>206</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7476,13 +7523,13 @@
         <v>232</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>235</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7496,13 +7543,13 @@
         <v>311</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7516,198 +7563,198 @@
         <v>317</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>368</v>
+        <v>138</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>133</v>
+        <v>369</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>386</v>
+        <v>181</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>181</v>
+        <v>392</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>417</v>
+        <v>181</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>432</v>
+        <v>145</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>436</v>
+        <v>138</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E41" s="4" t="s">
+      <c r="D42" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>470</v>
-      </c>
       <c r="F42" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>472</v>
@@ -7716,197 +7763,217 @@
         <v>473</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>476</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>492</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>496</v>
+        <v>138</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="C47" s="4" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>175</v>
+        <v>511</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>176</v>
+        <v>512</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>138</v>
+        <v>515</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>541</v>
+        <v>133</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>542</v>
+        <v>181</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>550</v>
+        <v>138</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="C53" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>622</v>
+      <c r="F53" s="4" t="s">
+        <v>628</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F53"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7942,16 +8009,16 @@
         <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>250</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7959,19 +8026,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A2,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"Easy")</f>
         <v>11</v>
       </c>
       <c r="C2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A2,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"Partly")</f>
         <v>1</v>
       </c>
       <c r="D2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A2,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A2,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F2" s="8" t="n">
@@ -7988,19 +8055,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A3,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A3,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A3,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A3,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
@@ -8017,19 +8084,19 @@
         <v>154</v>
       </c>
       <c r="B4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A4,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"Easy")</f>
         <v>2</v>
       </c>
       <c r="C4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A4,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A4,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A4,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F4" s="8" t="n">
@@ -8046,19 +8113,19 @@
         <v>186</v>
       </c>
       <c r="B5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A5,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"Easy")</f>
         <v>12</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A5,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A5,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A5,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"n/a")</f>
         <v>1</v>
       </c>
       <c r="F5" s="8" t="n">
@@ -8075,19 +8142,19 @@
         <v>252</v>
       </c>
       <c r="B6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A6,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"Easy")</f>
         <v>10</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A6,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"Partly")</f>
         <v>0</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A6,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A6,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"n/a")</f>
         <v>1</v>
       </c>
       <c r="F6" s="8" t="n">
@@ -8104,48 +8171,48 @@
         <v>290</v>
       </c>
       <c r="B7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A7,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"Easy")</f>
         <v>5</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A7,Criteria!$H$2:$H$140,"Partly")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"Partly")</f>
+        <v>3</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A7,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A7,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">IF(F7=0,0,B7/F7)</f>
-        <v>0.714285714285714</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A8,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"Easy")</f>
         <v>8</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A8,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"Partly")</f>
         <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A8,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A8,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
@@ -8159,22 +8226,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A9,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A9,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A9,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A9,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
@@ -8188,22 +8255,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A10,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A10,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A10,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A10,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
@@ -8217,22 +8284,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A11,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"Easy")</f>
         <v>8</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A11,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A11,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A11,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
@@ -8246,22 +8313,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A12,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"Easy")</f>
         <v>7</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A12,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A12,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A12,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
@@ -8275,22 +8342,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A13,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A13,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A13,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A13,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
@@ -8304,22 +8371,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A14,Criteria!$H$2:$H$140,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"Easy")</f>
         <v>4</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A14,Criteria!$H$2:$H$140,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A14,Criteria!$H$2:$H$140,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"No")</f>
         <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$140,$A14,Criteria!$H$2:$H$140,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
@@ -8333,7 +8400,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">SUM(B2:B14)</f>
@@ -8341,7 +8408,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">SUM(C2:C14)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">SUM(D2:D14)</f>
@@ -8353,16 +8420,16 @@
       </c>
       <c r="F15" s="10" t="n">
         <f aca="false">SUM(F2:F14)</f>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G15" s="11" t="n">
         <f aca="false">IF(F15=0,0,B15/F15)</f>
-        <v>0.741007194244604</v>
+        <v>0.735714285714286</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8370,7 +8437,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -8383,7 +8450,7 @@
         <v>75</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -8393,10 +8460,10 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -8409,7 +8476,7 @@
         <v>250</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -8419,10 +8486,10 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -8432,10 +8499,10 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>

--- a/docs/criteria/Screener_Criteria.xlsx
+++ b/docs/criteria/Screener_Criteria.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Criteria!$A$1:$I$141</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Unverifiable!$A$1:$F$53</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Criteria!$A$1:$I$158</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Unverifiable!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="717">
   <si>
     <t xml:space="preserve">Screen</t>
   </si>
@@ -1718,6 +1718,207 @@
     <t xml:space="preserve">Avg daily value traded &gt;= $1M</t>
   </si>
   <si>
+    <t xml:space="preserve">Tech S-Curve Leaders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIC 7370-7379 (software branch); 3570-3579, 3661-3679, 3825, 3827 (hardware branch); config allowlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Silver and David Tykocinski (Maverick) state that one screen should cover software and AI picks-and-shovels alike, because value in a technology wave moves between layers, "upstream" first and downstream later. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rules test economics, not the AI story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Sacerdote states that an S-curve shows up as growth and rising margins together, because "when you get scurve and a rising margin your earnings don't grow linearly they grow exponentially"; seeing both needs several years of numbers. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old numbers can hide a recent collapse; the screen needs the latest annual report. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the Emerging screen's size floor: tiny filers have patchy data and are hard to own. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Gerstner states that growth means value in technology, because "the single greatest input to valuation technology is growth". No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defining rule of the screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YTD (else latest FY) growth &gt;= 3-yr CAGR - 5 pts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Sacerdote states that a revenue miss means a broken tech stock, because "the biggest reason people blow up in Tech is they miss on revenue". Brad Gerstner adds that "every sell-side model on Wall Street has linear deceleration in growth rates", so a fade faster than that surprises the market. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catches the deceleration models assume away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule of 40 after stock pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-yr revenue CAGR + 3-yr (FCF - SBC) / revenue &gt;= 40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippe and Thomas Laffont (Coatue) state that growth plus profitability of 40 marks the strong cohort, because "growth in profitability yielding a rule of 40 was kind of the average of the cohort". Brad Gerstner and Bill Mylod state that stock pay is a real expense, so it is subtracted from free cash flow here. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth and cash generation in one test, net of stock pay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software &gt;= 70%; hardware: gross margin up over 3 yrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Levie states that a low gross margin means a software company can never earn software margins, because at "40 50 60% gross margin, like there's just like no way you're going to have an operating margin [that] looks like a software company". Maverick states that hardware is different: the "sharpest revision torque" came "frequently against companies that had very low margin basis", so for hardware the test is a rising margin. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room for software-like operating margins / pricing power.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating margin up over 3 yrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Sacerdote states that rising margins on an S-curve mean exponential earnings, because "when you get scurve and a rising margin your earnings don't grow linearly they grow exponentially". No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnings compound faster than sales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock pay vs free cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBC &lt;= 20% of FCF (3 yrs); FCF &lt;= 0 fails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital allocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Gerstner states that stock pay under a fifth of free cash flow marks a rare, disciplined company, because there are "maybe 10 names that are under 20% of their free cash flow as a percentage of stock-based compensation". Bill Mylod calls stock pay "the most single valuable expense". No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash flow belongs to shareholders, not staff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share count growth &lt;= 1%/yr (3 yrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill Mylod states that a shrinking share count turns business growth into a bigger share-price gain, because "if the enterprise value has doubled, the share price has tripled" for a company that bought back stock. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-share value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-funded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex &lt;= 100% of operating cash flow (3 yrs) and net debt / EBITDA &lt;= 2.0x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maverick states that today's AI build-out differs from the dot-com one because spending is "well under 100 percent" of operating cash flow. Gavin Baker asks whether spending is "funded out of debt or cash flows", and Bill Gurley warns that a "three to one ... debt to equity ratio" could be "a real painful ... downside". A mentioned example: the dot-com build-out versus today's cash-funded AI build-out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build-outs paid from own cash, not debt or new shares.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return on new capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-yr incremental ROIC &gt;= 15% (capital-light growth counts as a pass)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill Gurley states that growth spending must be judged by "what's the return on the incremental investment". Michael Mauboussin states that growth creates value only when companies "earn above the opportunity cost of capital". No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth that creates value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invested capital from balance-sheet tags; acquisitions distort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software: receivable days up &lt;= 10 over 3 yrs; hardware: inventory days not at a 5-yr high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill Gurley states that slipping receivables mean a company is pulling revenue forward, because "their DSO's are just slipping out". Gavin Baker states that piling inventory signals a bust, because before the 2000 chip crash "customer inventories and days inventory were at all-time highs". A mentioned example: chip stocks in 2000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early warning of channel stuffing or a demand air pocket.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market cap &gt;= $1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big enough to trade without moving the price. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg daily value traded &gt;= $5M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be able to build and exit a position. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / sales &lt;= 3-yr growth in points / 3 (30% -&gt; 10x), max 15x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill Gurley states that a high sales multiple needs high growth, because "if you want a 10x multiple you got be growing 30 35%". Leon Shaulov warns that winners "may not screen as the cheapest things in the world", so failing only this rule makes a 'wait for a better price' near miss. No specific past example given.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price justified by growth; failing only this = 'wait for a better price'.</t>
+  </si>
+  <si>
     <t xml:space="preserve">'Cheap enough' rule (pass/fail)</t>
   </si>
   <si>
@@ -1784,6 +1985,12 @@
     <t xml:space="preserve">EV/sales &gt;= 6x (expensive = flag)</t>
   </si>
   <si>
+    <t xml:space="preserve">EV/sales &lt;= growth points / 3, max 15x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth-adjusted multiple</t>
+  </si>
+  <si>
     <t xml:space="preserve">Answer: 9 of 13 screens have an absolute 'cheap enough' rule. None compares price to peers or to the company's own past multiples as a pass/fail rule.</t>
   </si>
   <si>
@@ -1899,6 +2106,12 @@
   </si>
   <si>
     <t xml:space="preserve">Short interest and insider-trade data not connected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moat, S-curve stage (adoption share), depreciation policy for compute, AI disruption risk. Excluded by choice (Oct 2026): market position, net retention, AI share of sales, customer concentration, China/Taiwan exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in XBRL financial data (dimensional or narrative).</t>
   </si>
   <si>
     <t xml:space="preserve">Kept (verifiable for most; gaps -&gt; Near misses with the reason)</t>
@@ -2523,7 +2736,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -6522,9 +6735,484 @@
       </c>
       <c r="I141" s="4"/>
     </row>
+    <row r="142" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I143" s="4"/>
+    </row>
+    <row r="144" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I145" s="4"/>
+    </row>
+    <row r="146" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="4"/>
+    </row>
+    <row r="147" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I147" s="4"/>
+    </row>
+    <row r="148" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I149" s="4"/>
+    </row>
+    <row r="150" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I150" s="4"/>
+    </row>
+    <row r="151" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="4"/>
+    </row>
+    <row r="153" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I155" s="4"/>
+    </row>
+    <row r="156" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I157" s="4"/>
+    </row>
+    <row r="158" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I141"/>
-  <conditionalFormatting sqref="H2:H141">
+  <autoFilter ref="A1:I158"/>
+  <conditionalFormatting sqref="H2:H158">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$H2="Easy"</formula>
     </cfRule>
@@ -6538,7 +7226,7 @@
       <formula>$H2="n/a"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:I141">
+  <conditionalFormatting sqref="A2:I158">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$E2="Valuation"</formula>
     </cfRule>
@@ -6559,7 +7247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -6575,19 +7263,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>563</v>
+        <v>630</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>566</v>
+        <v>633</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6595,19 +7283,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>568</v>
+        <v>635</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,19 +7303,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>572</v>
+        <v>639</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6635,19 +7323,19 @@
         <v>154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>574</v>
+        <v>641</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,19 +7343,19 @@
         <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6675,19 +7363,19 @@
         <v>252</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6695,19 +7383,19 @@
         <v>290</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>576</v>
+        <v>643</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>577</v>
+        <v>644</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6718,16 +7406,16 @@
         <v>356</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>578</v>
+        <v>645</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6735,19 +7423,19 @@
         <v>359</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>579</v>
+        <v>646</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6755,19 +7443,19 @@
         <v>395</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6775,19 +7463,19 @@
         <v>426</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>581</v>
+        <v>648</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>577</v>
+        <v>644</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6795,19 +7483,19 @@
         <v>457</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>582</v>
+        <v>649</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>583</v>
+        <v>650</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6815,19 +7503,19 @@
         <v>503</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>574</v>
+        <v>641</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6835,44 +7523,54 @@
         <v>539</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>584</v>
+        <v>651</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>587</v>
+        <v>655</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -6880,11 +7578,21 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6901,7 +7609,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -6920,16 +7628,16 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>588</v>
+        <v>657</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>589</v>
+        <v>658</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>590</v>
+        <v>659</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>591</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6937,19 +7645,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>592</v>
+        <v>661</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>593</v>
+        <v>662</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>595</v>
+        <v>664</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>596</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6957,19 +7665,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>597</v>
+        <v>666</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>598</v>
+        <v>667</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6977,19 +7685,19 @@
         <v>82</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>602</v>
+        <v>671</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6997,19 +7705,19 @@
         <v>154</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>603</v>
+        <v>672</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>604</v>
+        <v>673</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7017,19 +7725,19 @@
         <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>605</v>
+        <v>674</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>606</v>
+        <v>675</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>595</v>
+        <v>664</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>607</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7037,19 +7745,19 @@
         <v>186</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>608</v>
+        <v>677</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7057,19 +7765,19 @@
         <v>252</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>605</v>
+        <v>674</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>606</v>
+        <v>675</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>595</v>
+        <v>664</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>607</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7077,19 +7785,19 @@
         <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>609</v>
+        <v>678</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>610</v>
+        <v>679</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7097,19 +7805,19 @@
         <v>290</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>611</v>
+        <v>680</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>612</v>
+        <v>681</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7117,19 +7825,19 @@
         <v>325</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>613</v>
+        <v>682</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>614</v>
+        <v>683</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7137,19 +7845,19 @@
         <v>359</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>605</v>
+        <v>674</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>606</v>
+        <v>675</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>595</v>
+        <v>664</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>607</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7157,19 +7865,19 @@
         <v>359</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>615</v>
+        <v>684</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>616</v>
+        <v>685</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7177,19 +7885,19 @@
         <v>395</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>617</v>
+        <v>686</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,19 +7905,19 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>618</v>
+        <v>687</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7217,19 +7925,19 @@
         <v>457</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>619</v>
+        <v>688</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7237,19 +7945,19 @@
         <v>503</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>620</v>
+        <v>689</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>621</v>
+        <v>690</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7257,59 +7965,59 @@
         <v>539</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>622</v>
+        <v>691</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>594</v>
+        <v>663</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>623</v>
+        <v>692</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="D20" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="F20" s="4" t="s">
-        <v>626</v>
+        <v>696</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7317,39 +8025,39 @@
         <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>628</v>
+        <v>698</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7357,19 +8065,19 @@
         <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7377,39 +8085,39 @@
         <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>627</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7417,19 +8125,19 @@
         <v>154</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>627</v>
+        <v>698</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7437,79 +8145,79 @@
         <v>154</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D30" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>625</v>
+        <v>699</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7517,39 +8225,39 @@
         <v>186</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="D32" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="F32" s="4" t="s">
-        <v>628</v>
+        <v>701</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7557,19 +8265,19 @@
         <v>290</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>316</v>
+        <v>133</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7577,79 +8285,79 @@
         <v>290</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>373</v>
+        <v>138</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>359</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>369</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>628</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7657,39 +8365,39 @@
         <v>359</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>392</v>
+        <v>181</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>181</v>
+        <v>392</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7697,79 +8405,79 @@
         <v>395</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>423</v>
+        <v>181</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>438</v>
+        <v>145</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>442</v>
+        <v>138</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>426</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="D43" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>476</v>
-      </c>
       <c r="F43" s="4" t="s">
-        <v>632</v>
+        <v>699</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7777,39 +8485,39 @@
         <v>457</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>628</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7817,79 +8525,79 @@
         <v>457</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>133</v>
+        <v>486</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>497</v>
+        <v>133</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>502</v>
+        <v>138</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>627</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>503</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>175</v>
+        <v>511</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>176</v>
+        <v>512</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>138</v>
+        <v>515</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>628</v>
+        <v>704</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7897,83 +8605,203 @@
         <v>503</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>539</v>
+        <v>503</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>547</v>
+        <v>133</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>548</v>
+        <v>181</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>539</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>624</v>
+        <v>695</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>556</v>
+        <v>138</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>539</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="D54" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>628</v>
+      <c r="F54" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:F59"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7990,7 +8818,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -8009,16 +8837,16 @@
         <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>571</v>
+        <v>638</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>250</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>634</v>
+        <v>705</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>635</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8026,19 +8854,19 @@
         <v>9</v>
       </c>
       <c r="B2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A2,Criteria!$H$2:$H$158,"Easy")</f>
         <v>11</v>
       </c>
       <c r="C2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A2,Criteria!$H$2:$H$158,"Partly")</f>
         <v>1</v>
       </c>
       <c r="D2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A2,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E2" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A2,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A2,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F2" s="8" t="n">
@@ -8055,19 +8883,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A3,Criteria!$H$2:$H$158,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A3,Criteria!$H$2:$H$158,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A3,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A3,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A3,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
@@ -8084,19 +8912,19 @@
         <v>154</v>
       </c>
       <c r="B4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A4,Criteria!$H$2:$H$158,"Easy")</f>
         <v>2</v>
       </c>
       <c r="C4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A4,Criteria!$H$2:$H$158,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A4,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E4" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A4,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A4,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F4" s="8" t="n">
@@ -8113,19 +8941,19 @@
         <v>186</v>
       </c>
       <c r="B5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A5,Criteria!$H$2:$H$158,"Easy")</f>
         <v>12</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A5,Criteria!$H$2:$H$158,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A5,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E5" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A5,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A5,Criteria!$H$2:$H$158,"n/a")</f>
         <v>1</v>
       </c>
       <c r="F5" s="8" t="n">
@@ -8142,19 +8970,19 @@
         <v>252</v>
       </c>
       <c r="B6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A6,Criteria!$H$2:$H$158,"Easy")</f>
         <v>10</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A6,Criteria!$H$2:$H$158,"Partly")</f>
         <v>0</v>
       </c>
       <c r="D6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A6,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A6,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A6,Criteria!$H$2:$H$158,"n/a")</f>
         <v>1</v>
       </c>
       <c r="F6" s="8" t="n">
@@ -8171,19 +8999,19 @@
         <v>290</v>
       </c>
       <c r="B7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A7,Criteria!$H$2:$H$158,"Easy")</f>
         <v>5</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A7,Criteria!$H$2:$H$158,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A7,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A7,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A7,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
@@ -8200,19 +9028,19 @@
         <v>325</v>
       </c>
       <c r="B8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A8,Criteria!$H$2:$H$158,"Easy")</f>
         <v>8</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A8,Criteria!$H$2:$H$158,"Partly")</f>
         <v>1</v>
       </c>
       <c r="D8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A8,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A8,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A8,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
@@ -8229,19 +9057,19 @@
         <v>359</v>
       </c>
       <c r="B9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A9,Criteria!$H$2:$H$158,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A9,Criteria!$H$2:$H$158,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A9,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A9,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A9,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
@@ -8258,19 +9086,19 @@
         <v>395</v>
       </c>
       <c r="B10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A10,Criteria!$H$2:$H$158,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A10,Criteria!$H$2:$H$158,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A10,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A10,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A10,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
@@ -8287,19 +9115,19 @@
         <v>426</v>
       </c>
       <c r="B11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A11,Criteria!$H$2:$H$158,"Easy")</f>
         <v>8</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A11,Criteria!$H$2:$H$158,"Partly")</f>
         <v>2</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A11,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A11,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A11,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
@@ -8316,19 +9144,19 @@
         <v>457</v>
       </c>
       <c r="B12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A12,Criteria!$H$2:$H$158,"Easy")</f>
         <v>7</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A12,Criteria!$H$2:$H$158,"Partly")</f>
         <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A12,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A12,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A12,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
@@ -8345,19 +9173,19 @@
         <v>503</v>
       </c>
       <c r="B13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A13,Criteria!$H$2:$H$158,"Easy")</f>
         <v>9</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A13,Criteria!$H$2:$H$158,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A13,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A13,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A13,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
@@ -8374,19 +9202,19 @@
         <v>539</v>
       </c>
       <c r="B14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"Easy")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A14,Criteria!$H$2:$H$158,"Easy")</f>
         <v>4</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"Partly")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A14,Criteria!$H$2:$H$158,"Partly")</f>
         <v>3</v>
       </c>
       <c r="D14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"No")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A14,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <f aca="false">COUNTIFS(Criteria!$A$2:$A$141,$A14,Criteria!$H$2:$H$141,"n/a")</f>
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A14,Criteria!$H$2:$H$158,"n/a")</f>
         <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
@@ -8400,57 +9228,73 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <f aca="false">SUM(B2:B14)</f>
-        <v>103</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <f aca="false">SUM(C2:C14)</f>
-        <v>35</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <f aca="false">SUM(D2:D14)</f>
+        <v>563</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A15,Criteria!$H$2:$H$158,"Easy")</f>
+        <v>12</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A15,Criteria!$H$2:$H$158,"Partly")</f>
+        <v>5</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A15,Criteria!$H$2:$H$158,"No")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <f aca="false">SUM(E2:E14)</f>
+      <c r="E15" s="8" t="n">
+        <f aca="false">COUNTIFS(Criteria!$A$2:$A$158,$A15,Criteria!$H$2:$H$158,"n/a")</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <f aca="false">SUM(B15:E15)</f>
+        <v>17</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">IF(F15=0,0,B15/F15)</f>
+        <v>0.705882352941177</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="B16" s="10" t="n">
+        <f aca="false">SUM(B2:B15)</f>
+        <v>115</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <f aca="false">SUM(C2:C15)</f>
+        <v>40</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <f aca="false">SUM(D2:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <f aca="false">SUM(E2:E15)</f>
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <f aca="false">SUM(F2:F14)</f>
-        <v>140</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <f aca="false">IF(F15=0,0,B15/F15)</f>
-        <v>0.735714285714286</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="F16" s="10" t="n">
+        <f aca="false">SUM(F2:F15)</f>
+        <v>157</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <f aca="false">IF(F16=0,0,B16/F16)</f>
+        <v>0.732484076433121</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>75</v>
+      <c r="A19" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>639</v>
+        <v>709</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -8459,11 +9303,11 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>571</v>
+      <c r="A20" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>640</v>
+        <v>710</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -8472,11 +9316,11 @@
       <c r="G20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>250</v>
+      <c r="A21" s="15" t="s">
+        <v>638</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>641</v>
+        <v>711</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -8485,11 +9329,11 @@
       <c r="G21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>642</v>
+      <c r="A22" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>643</v>
+        <v>712</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -8499,10 +9343,10 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>644</v>
+        <v>713</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -8510,14 +9354,27 @@
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
